--- a/output/Shandong/日照市_news.xlsx
+++ b/output/Shandong/日照市_news.xlsx
@@ -551,9 +551,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>True</t>
@@ -565,14 +563,12 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>285</v>
+        <v>465</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/aaa32360b0c34af1b775b068eb2b2766/detail</t>
@@ -621,9 +617,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>True</t>
@@ -635,14 +629,12 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>16669</v>
+        <v>16858</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/37a0da7e9dad428badd94b8e47f2dbee/detail</t>
@@ -691,9 +683,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>True</t>
@@ -705,14 +695,12 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>16320</v>
+        <v>16508</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/0a71a6c7e2a843859b463b0a06c1b87b/detail</t>
@@ -761,9 +749,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>True</t>
@@ -775,14 +761,12 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6060</v>
+        <v>6266</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/1dcaa59859c6454696279130a5d33114/detail</t>
@@ -831,9 +815,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>True</t>
@@ -845,14 +827,12 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9140</v>
+        <v>9319</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/6cfb33ae2712424b8f8124e988afd6c8/detail</t>
@@ -901,9 +881,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>True</t>
@@ -915,14 +893,12 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>9795</v>
+        <v>9969</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/7296868243554c689207742366af0ed3/detail</t>
@@ -971,9 +947,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>True</t>
@@ -985,14 +959,12 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9158</v>
+        <v>9329</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/60ef0faad8ac44659c514cb28829806b/detail</t>
@@ -1041,9 +1013,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>True</t>
@@ -1055,14 +1025,12 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8994</v>
+        <v>9172</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/6d2327fa5ecc4a839f42749ae39d4d27/detail</t>
@@ -1111,9 +1079,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>True</t>
@@ -1125,14 +1091,12 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9300</v>
+        <v>9473</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/dd297f08ed4b42cc8e1edafbe90d9880/detail</t>
@@ -1181,9 +1145,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>True</t>
@@ -1195,14 +1157,12 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>9318</v>
+        <v>9494</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/df5e830e6b4e4256b4d455fced1055ad/detail</t>
@@ -1251,9 +1211,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>True</t>
@@ -1265,14 +1223,12 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9761</v>
+        <v>9780</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/023320e58bb24514b5a3f686a5da2bb8/detail</t>
@@ -1321,9 +1277,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>True</t>
@@ -1335,14 +1289,12 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7870</v>
+        <v>7891</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/6324d30635674f7484bc893af024abc9/detail</t>
@@ -1391,9 +1343,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>True</t>
@@ -1405,14 +1355,12 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>9221</v>
+        <v>9281</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/44deb96028b3424b8de6bf03cc919666/detail</t>
@@ -1461,9 +1409,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>True</t>
@@ -1475,14 +1421,12 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4482</v>
+        <v>4506</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/95558ca3c79042c08135d73c7ab2c329/detail</t>
@@ -1531,9 +1475,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>True</t>
@@ -1545,14 +1487,12 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>992</v>
+        <v>1025</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/12b2bdcfc4794edbac2faf11f07e8dbe/detail</t>
@@ -1601,9 +1541,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>True</t>
@@ -1615,14 +1553,12 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/4581485a0c3045fdbb72308d8ed13e6a/detail</t>
@@ -1671,9 +1607,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>True</t>
@@ -1685,14 +1619,12 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>811</v>
+        <v>842</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/a325aad99aac4f14a1b0fe51d0c27ecb/detail</t>
@@ -1741,9 +1673,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>True</t>
@@ -1755,14 +1685,12 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/0d92a0a24cb242d9858b7b6ed426d21d/detail</t>
@@ -1811,9 +1739,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>True</t>
@@ -1825,14 +1751,12 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>666</v>
+        <v>695</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/2bb2d67e3d8b4948908a697183444c6a/detail</t>
@@ -1881,9 +1805,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>True</t>
@@ -1895,14 +1817,12 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/d9d546ae404747d99351f8cc277551e0/detail</t>
@@ -1951,9 +1871,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>True</t>
@@ -1965,14 +1883,12 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/c7d5bd901cd94a4bb36b9357cb8a60a3/detail</t>
@@ -2021,9 +1937,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>True</t>
@@ -2035,14 +1949,12 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>650</v>
+        <v>664</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ec11bb754fe242e68fddfe6c50f98f33/detail</t>
@@ -2091,9 +2003,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>True</t>
@@ -2105,14 +2015,12 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ccb6e97c832c459a95f87f1cee22088f/detail</t>
@@ -2128,7 +2036,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>东港区交通运输局行政处罚裁量权清单数据量查询服务</t>
+          <t>东港区交通运输局行政处罚裁量权清单分页查询服务</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2138,7 +2046,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>东港区交通运输局行政处罚裁量权清单数据量查询服务</t>
+          <t>东港区交通运输局行政处罚裁量权清单分页查询服务</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2161,9 +2069,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>True</t>
@@ -2175,17 +2081,15 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>13979</v>
+        <v>9851</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/77478b1dc3854d0db1201084a91fb292/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/3c7b02732116471ca3dcaa10ae9e5557/detail</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2198,7 +2102,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>东港区交通运输局行政处罚裁量权清单分页查询服务</t>
+          <t>东港区交通运输局行政处罚裁量权清单数据量查询服务</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2208,7 +2112,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>东港区交通运输局行政处罚裁量权清单分页查询服务</t>
+          <t>东港区交通运输局行政处罚裁量权清单数据量查询服务</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2231,9 +2135,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>True</t>
@@ -2245,17 +2147,15 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9818</v>
+        <v>14010</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3c7b02732116471ca3dcaa10ae9e5557/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/77478b1dc3854d0db1201084a91fb292/detail</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2301,9 +2201,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>True</t>
@@ -2315,14 +2213,12 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>13945</v>
+        <v>13977</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/0bf3ddaf601048279b98d434b13e517c/detail</t>
@@ -2371,9 +2267,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>True</t>
@@ -2385,14 +2279,12 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>9178</v>
+        <v>9246</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/bf8c045abcb14ccdbbaa54a1a2ebedc2/detail</t>
@@ -2441,9 +2333,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>True</t>
@@ -2455,14 +2345,12 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>8196</v>
+        <v>8204</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/3a8b740812e64675bf694adb854f015c/detail</t>
@@ -2511,9 +2399,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>True</t>
@@ -2525,14 +2411,12 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>7121</v>
+        <v>7205</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/d653f9ce79c848f885bdcf0eb04cc4d6/detail</t>
@@ -2581,9 +2465,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>True</t>
@@ -2595,14 +2477,12 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>7606</v>
+        <v>7645</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/9ed688b0ac514d0d9dc16d544b8a9b80/detail</t>
@@ -2651,9 +2531,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>True</t>
@@ -2665,14 +2543,12 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2505</v>
+        <v>2533</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/c4e5c29d828640f3bbdffdff9b53eaf7/detail</t>
@@ -2721,9 +2597,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>True</t>
@@ -2735,14 +2609,12 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1617</v>
+        <v>1632</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/acac2a2b2d2541779384cf67604e9757/detail</t>
@@ -2791,9 +2663,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>True</t>
@@ -2805,14 +2675,12 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1589</v>
+        <v>1614</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/79d07910dad84e4d9269e5a82453ab71/detail</t>
@@ -2861,9 +2729,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>True</t>
@@ -2875,14 +2741,12 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1687</v>
+        <v>1692</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/e878b00e4f5248bcb882daa57dde30aa/detail</t>
@@ -2931,9 +2795,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>True</t>
@@ -2945,14 +2807,12 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2638</v>
+        <v>2666</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/a5349f1250d44b4abaec31a283513c11/detail</t>
@@ -3001,9 +2861,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>True</t>
@@ -3015,14 +2873,12 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2949</v>
+        <v>2984</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/1a4fbd5b0d3149419db8aac2e688b660/detail</t>
@@ -3071,9 +2927,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>True</t>
@@ -3085,14 +2939,12 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/f37647faa32e40e399f05e286ba342b3/detail</t>
@@ -3141,9 +2993,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>True</t>
@@ -3155,14 +3005,12 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1957</v>
+        <v>1964</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/5f6619c132af49959a8b218e38e58534/detail</t>
@@ -3211,9 +3059,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>True</t>
@@ -3225,14 +3071,12 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/adbd4219885248a7970c99a9389462dd/detail</t>
@@ -3281,9 +3125,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>True</t>
@@ -3295,14 +3137,12 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/5853a176dc2049f48e96473415fcc4c8/detail</t>
@@ -3351,9 +3191,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>True</t>
@@ -3365,14 +3203,12 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/03d3d410d74a417fb06d14b5f605238b/detail</t>
@@ -3421,9 +3257,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>True</t>
@@ -3435,14 +3269,12 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/07ec6c80c0a14a95b0c1cbdc0a660be7/detail</t>
@@ -3491,9 +3323,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>True</t>
@@ -3505,14 +3335,12 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/bf583b21da7644e38549e4cbf974c767/detail</t>
@@ -3561,9 +3389,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>True</t>
@@ -3575,14 +3401,12 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1150</v>
+        <v>1180</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/b73a0e84bbb34162b9475d874fb44ec7/detail</t>
@@ -3631,9 +3455,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>True</t>
@@ -3645,14 +3467,12 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/96931e1b4a6249988a3567bceb7536fc/detail</t>
@@ -3701,9 +3521,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>True</t>
@@ -3715,14 +3533,12 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/2057f7b72e3a411db82bbe10fedb4744/detail</t>
@@ -3771,9 +3587,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>True</t>
@@ -3785,14 +3599,12 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/7242dbef4aaa48cabf9da2ccf278638b/detail</t>
@@ -3841,9 +3653,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>True</t>
@@ -3855,14 +3665,12 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1310</v>
+        <v>1321</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/975e55139ea84013abd3b96c618982af/detail</t>
@@ -3911,9 +3719,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>True</t>
@@ -3925,14 +3731,12 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ea749c476e254138b06cd3277b20a528/detail</t>
@@ -3981,9 +3785,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>True</t>
@@ -3995,14 +3797,12 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/e790c49bc36f4b2e976e306ea56b2585/detail</t>
@@ -4051,9 +3851,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>True</t>
@@ -4065,14 +3863,12 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/f8180c7e0381470788dade44b0e90b56/detail</t>
@@ -4121,9 +3917,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>True</t>
@@ -4135,14 +3929,12 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/09579d76ba7b48c987c81449eab8ea03/detail</t>
@@ -4191,9 +3983,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>True</t>
@@ -4205,14 +3995,12 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1561</v>
+        <v>1719</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/2423d90787af474794307e232bbe4a71/detail</t>
@@ -4261,9 +4049,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>True</t>
@@ -4275,14 +4061,12 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/36b0ad21e00f41de84a2633af8211c06/detail</t>
@@ -4331,9 +4115,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>True</t>
@@ -4345,14 +4127,12 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1409</v>
+        <v>1426</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/8d8b311b97114e0dab95acaa250a5893/detail</t>
@@ -4401,9 +4181,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>True</t>
@@ -4415,14 +4193,12 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1554</v>
+        <v>1585</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/5afcf939ea084765aef2bfcc847700bb/detail</t>
@@ -4471,9 +4247,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>True</t>
@@ -4485,14 +4259,12 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1496</v>
+        <v>1518</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/7e6642bda6a1478fa24051bf76ad8669/detail</t>
@@ -4541,9 +4313,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>True</t>
@@ -4555,14 +4325,12 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>907</v>
+        <v>942</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/8a5df3b510454fbc8964a278c913b6f3/detail</t>
@@ -4611,9 +4379,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>True</t>
@@ -4625,14 +4391,12 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1594</v>
+        <v>1630</v>
       </c>
       <c r="M60" t="n">
         <v>1</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/9cff8848ea24460d83483253e6a2774c/detail</t>
@@ -4648,17 +4412,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>市政设施建设类审批分页查询服务</t>
+          <t>商品房预售许可证核发分页查询服务</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>信用服务</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>市政设施建设类审批分页查询服务</t>
+          <t>商品房预售许可证核发分页查询服务</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4681,9 +4445,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>True</t>
@@ -4695,17 +4457,15 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1476</v>
+        <v>384</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/8cc0292599914f95b75224d5d811fa25/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5e3790a665874d8f9844aca96a41ae3c/detail</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -4751,9 +4511,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>True</t>
@@ -4765,14 +4523,12 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/5e3790a665874d8f9844aca96a41ae3c/detail</t>
@@ -4821,9 +4577,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>True</t>
@@ -4835,14 +4589,12 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/dae61377fa0247e89215a59ccca8f737/detail</t>
@@ -4891,9 +4643,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>True</t>
@@ -4905,14 +4655,12 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/0444dd73a16e40f7bd507a37a043858e/detail</t>
@@ -4961,9 +4709,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>True</t>
@@ -4975,14 +4721,12 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/825f7acab2f84627ba6d524f399ea126/detail</t>
@@ -5031,9 +4775,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>True</t>
@@ -5045,14 +4787,12 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/4c7aa02ab0b54ad4ae763268932fcb09/detail</t>
@@ -5101,9 +4841,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>True</t>
@@ -5115,14 +4853,12 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1559</v>
+        <v>1562</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/293e9506c9f547a69a6e51cecf2c48ac/detail</t>
@@ -5171,9 +4907,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>True</t>
@@ -5185,14 +4919,12 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1259</v>
+        <v>1297</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/5663e238242046a1af6e50677a2ac2c2/detail</t>
@@ -5241,9 +4973,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>True</t>
@@ -5255,14 +4985,12 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1203</v>
+        <v>1220</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/941a8d389e7c4d289ada6f0cbeec2bcb/detail</t>
@@ -5311,9 +5039,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>True</t>
@@ -5325,14 +5051,12 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/9bdd7e8427734193a0ee952b433a9ec5/detail</t>
@@ -5381,9 +5105,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>True</t>
@@ -5395,14 +5117,12 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/a172dd93df9345d59ae7e32a26415f03/detail</t>
@@ -5451,9 +5171,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>True</t>
@@ -5465,14 +5183,12 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1074</v>
+        <v>1105</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/bc36c038a1914cbc9facc8a68cf27cdc/detail</t>
@@ -5521,9 +5237,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>True</t>
@@ -5535,14 +5249,12 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/50370cbf243e4aaa89d1eda100666d7f/detail</t>
@@ -5591,9 +5303,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>True</t>
@@ -5605,14 +5315,12 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1195</v>
+        <v>1225</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
       </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/000d25c2ec894f5c896fa897c0a6247a/detail</t>
@@ -5661,9 +5369,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>True</t>
@@ -5675,14 +5381,12 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/00aa5f5bb77f4481950e7d4b58bce5ad/detail</t>
@@ -5698,7 +5402,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>岚山区历年金融机构本外币贷款余额分页查询服务</t>
+          <t>岚山区历年金融机构本外币存款余额分页查询服务</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5708,7 +5412,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>岚山区历年金融机构本外币贷款余额分页查询服务</t>
+          <t>岚山区历年金融机构本外币存款余额分页查询服务</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5731,9 +5435,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>True</t>
@@ -5745,17 +5447,15 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e3923a899986498da8e759f799a2bd3b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/77a16728deae4326916bfd5eec0877e1/detail</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
@@ -5768,7 +5468,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>岚山区历年金融机构本外币存款余额分页查询服务</t>
+          <t>岚山区历年金融机构本外币贷款余额分页查询服务</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5778,7 +5478,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>岚山区历年金融机构本外币存款余额分页查询服务</t>
+          <t>岚山区历年金融机构本外币贷款余额分页查询服务</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5801,9 +5501,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>True</t>
@@ -5815,17 +5513,15 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/77a16728deae4326916bfd5eec0877e1/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e3923a899986498da8e759f799a2bd3b/detail</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
@@ -5871,9 +5567,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>True</t>
@@ -5885,14 +5579,12 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/44aebc32a16247a394cb9a7fde896718/detail</t>
@@ -5941,9 +5633,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>True</t>
@@ -5955,14 +5645,12 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/c9f7693a6e2a478d9f4a8de19e5ae3ea/detail</t>
@@ -6011,9 +5699,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>True</t>
@@ -6025,14 +5711,12 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/3e739fd13c5745ee9a3ea0182bb6a9da/detail</t>
@@ -6048,7 +5732,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>岚山区历年社会消费品零售总额分页查询服务</t>
+          <t>岚山区历年固定资产投资分页查询服务</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6058,7 +5742,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>岚山区历年社会消费品零售总额分页查询服务</t>
+          <t>岚山区历年固定资产投资分页查询服务</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6081,9 +5765,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>True</t>
@@ -6095,17 +5777,15 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a80e55e424cc4305bb04dcdadda0f1d1/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/4c0db3725d6047cf944c0b9b1d9e743d/detail</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -6151,9 +5831,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>True</t>
@@ -6165,14 +5843,12 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/a80e55e424cc4305bb04dcdadda0f1d1/detail</t>
@@ -6221,9 +5897,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>True</t>
@@ -6235,14 +5909,12 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>828</v>
+        <v>844</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/58b2162f7b56454fa0ba1f7f51f11424/detail</t>
@@ -6291,9 +5963,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>True</t>
@@ -6305,14 +5975,12 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1310</v>
+        <v>1340</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/41eb5e0c9e864b55af4788f35542e4db/detail</t>
@@ -6361,9 +6029,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>True</t>
@@ -6375,14 +6041,12 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1385</v>
+        <v>1420</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/f2ffb537369247dcb2034083aff1fd49/detail</t>
@@ -6398,7 +6062,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>岚山区历年一般公共预算收入分页查询服务</t>
+          <t>岚山区历年一般公共预算支出分页查询服务</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6408,7 +6072,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>岚山区历年一般公共预算收入分页查询服务</t>
+          <t>岚山区历年一般公共预算支出分页查询服务</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6431,9 +6095,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>True</t>
@@ -6445,17 +6107,15 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b9d0465820b2463788579297b6c9aca2/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/62d2b0c2e2a143f8a6ecd69c40c88e5e/detail</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -6468,7 +6128,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>岚山区历年一般公共预算支出分页查询服务</t>
+          <t>岚山区历年一般公共预算收入分页查询服务</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6478,7 +6138,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>岚山区历年一般公共预算支出分页查询服务</t>
+          <t>岚山区历年一般公共预算收入分页查询服务</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6501,9 +6161,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>True</t>
@@ -6515,17 +6173,15 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/62d2b0c2e2a143f8a6ecd69c40c88e5e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b9d0465820b2463788579297b6c9aca2/detail</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
@@ -6571,9 +6227,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>True</t>
@@ -6585,14 +6239,12 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1089</v>
+        <v>1100</v>
       </c>
       <c r="M88" t="n">
         <v>1</v>
       </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/3801e5086f5b45c9baec124387dfbe96/detail</t>
@@ -6641,9 +6293,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>True</t>
@@ -6655,14 +6305,12 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/d050ce708c044828bf057539357cc532/detail</t>
@@ -6711,9 +6359,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>True</t>
@@ -6725,14 +6371,12 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M90" t="n">
         <v>1</v>
       </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/efc019cef0b14e9e8daaa3ccd49085bf/detail</t>
@@ -6781,9 +6425,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>True</t>
@@ -6795,14 +6437,12 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/82a10341239945dc8f4809b6c8e27a31/detail</t>
@@ -6851,9 +6491,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>True</t>
@@ -6865,14 +6503,12 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/69a0546261314ac69ff1bb708ea67a34/detail</t>
@@ -6921,9 +6557,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>True</t>
@@ -6935,14 +6569,12 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1368</v>
+        <v>1374</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/717acbc1b1db426da31d7d142be224c3/detail</t>
@@ -6991,9 +6623,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>True</t>
@@ -7005,14 +6635,12 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1615</v>
+        <v>1623</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/5e7b2f8351dd4e1cb6e03453734205d7/detail</t>
@@ -7061,9 +6689,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>True</t>
@@ -7075,14 +6701,12 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/72fd8ccb8fde45c6bab9c75b54d4fbe8/detail</t>
@@ -7131,9 +6755,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>True</t>
@@ -7145,14 +6767,12 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1427</v>
+        <v>1432</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/6cb3146a701e46959b45979801b5d628/detail</t>
@@ -7201,9 +6821,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>True</t>
@@ -7215,14 +6833,12 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/59d33eb1405845ef98386630c4323f4c/detail</t>
@@ -7271,9 +6887,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>True</t>
@@ -7285,14 +6899,12 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1421</v>
+        <v>1440</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/7cf32d22af3e463da0300ed6947852a4/detail</t>
@@ -7341,9 +6953,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>True</t>
@@ -7355,14 +6965,12 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>976</v>
+        <v>998</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/794e7a6fe4a54c529afeabde2f330626/detail</t>
@@ -7411,9 +7019,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>True</t>
@@ -7425,14 +7031,12 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>13478</v>
+        <v>13623</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/c060f4345148453dab27b6f6ea6ca23c/detail</t>
@@ -7481,9 +7085,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>True</t>
@@ -7495,14 +7097,12 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>16305</v>
+        <v>16453</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/9627e9927d1041d3bf1e24453d85daa5/detail</t>
@@ -7551,9 +7151,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>True</t>
@@ -7565,14 +7163,12 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>22871</v>
+        <v>23030</v>
       </c>
       <c r="M102" t="n">
         <v>1</v>
       </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/6776765448af40d9a10e261db1425491/detail</t>
@@ -7621,9 +7217,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>True</t>
@@ -7635,14 +7229,12 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/ef8196cb85f546bf8e414ce35502cfc3/detail</t>
@@ -7691,9 +7283,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>True</t>
@@ -7705,14 +7295,12 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/147889b51d194e4992285a4358d4ed6e/detail</t>
@@ -7761,9 +7349,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>True</t>
@@ -7775,14 +7361,12 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1151</v>
+        <v>1163</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
       </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/2b73b5d9504c447f86838383f6516fde/detail</t>
@@ -7831,9 +7415,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>True</t>
@@ -7845,14 +7427,12 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
       </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/dc1e27eaa8c34fc19f99fa631c75e155/detail</t>
@@ -7868,17 +7448,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>东港区星级酒店名单分页查询服务</t>
+          <t>机动车维修业户信息分页查询服务</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>资源环境</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>东港区星级酒店名单分页查询服务</t>
+          <t>机动车维修业户信息分页查询服务</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7901,9 +7481,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>True</t>
@@ -7915,17 +7493,15 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>156</v>
+        <v>1082</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
       </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d71df13691c345739f1661942e46b05a/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5b63515ff9954382957063db3a9ad19f/detail</t>
         </is>
       </c>
       <c r="P107" t="inlineStr"/>
@@ -7938,17 +7514,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>机动车维修业户信息分页查询服务</t>
+          <t>东港区星级酒店名单分页查询服务</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>机动车维修业户信息分页查询服务</t>
+          <t>东港区星级酒店名单分页查询服务</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7971,9 +7547,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>True</t>
@@ -7985,17 +7559,15 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1073</v>
+        <v>163</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
       </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5b63515ff9954382957063db3a9ad19f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d71df13691c345739f1661942e46b05a/detail</t>
         </is>
       </c>
       <c r="P108" t="inlineStr"/>
@@ -8041,9 +7613,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>True</t>
@@ -8055,14 +7625,12 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
       </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/6140e829021d481fa690330f71f54bfd/detail</t>
@@ -8111,9 +7679,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>True</t>
@@ -8125,14 +7691,12 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
       </c>
-      <c r="N110" t="n">
-        <v>0</v>
-      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/acc98a1081b54b0596ee86dcc1de9c3b/detail</t>
@@ -8181,9 +7745,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>True</t>
@@ -8195,14 +7757,12 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1485</v>
+        <v>1515</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
       </c>
-      <c r="N111" t="n">
-        <v>0</v>
-      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/4f9ad9a04ed0452ba4e706f77699f95d/detail</t>
@@ -8251,9 +7811,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>True</t>
@@ -8265,14 +7823,12 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
       </c>
-      <c r="N112" t="n">
-        <v>0</v>
-      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/290d48567bd74570bdafa18826c3ed8c/detail</t>
@@ -8321,9 +7877,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>True</t>
@@ -8335,14 +7889,12 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/6c88bf65bc0848369965f7642a622739/detail</t>
@@ -8391,9 +7943,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>True</t>
@@ -8405,14 +7955,12 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
       </c>
-      <c r="N114" t="n">
-        <v>0</v>
-      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/dd7b889fdad44406aac9267fd5d94076/detail</t>
@@ -8461,9 +8009,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>True</t>
@@ -8475,14 +8021,12 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
       </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/09ae2f3af1a84143bea3779e25727e2d/detail</t>
@@ -8531,9 +8075,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>True</t>
@@ -8545,14 +8087,12 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/feaaf7fb00354b029a7261a85b57a569/detail</t>
@@ -8601,9 +8141,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>True</t>
@@ -8615,14 +8153,12 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
       </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/4f44a894d5ee4897a956fdbef0ca229f/detail</t>
@@ -8671,9 +8207,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>True</t>
@@ -8685,14 +8219,12 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2318</v>
+        <v>2352</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
       </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/1c46a93ef268489a8c1443bf2da18bcf/detail</t>
@@ -8741,9 +8273,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>True</t>
@@ -8755,14 +8285,12 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
       </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/bb7c5b3489294defa75c5154fa5729ca/detail</t>
@@ -8811,9 +8339,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>True</t>
@@ -8825,14 +8351,12 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
       </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/aeb9a7047b9c453d9ff8fbaad3322569/detail</t>
@@ -8881,9 +8405,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>True</t>
@@ -8895,14 +8417,12 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
       </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/b592cc35472f4c0f87589f2d3719bbde/detail</t>
@@ -8951,9 +8471,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>True</t>
@@ -8965,14 +8483,12 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1138</v>
+        <v>1162</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
       </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/8ae9a8ad5b6b40fbb046571b9ae22e4a/detail</t>
@@ -9021,9 +8537,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>True</t>
@@ -9035,14 +8549,12 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1632</v>
+        <v>1680</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/6bb22c3a118743f79e0b29e783c076f1/detail</t>
@@ -9091,9 +8603,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>True</t>
@@ -9105,14 +8615,12 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>863</v>
+        <v>882</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
       </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/193f2a18867346c9ab7eb6a75537941b/detail</t>
@@ -9161,9 +8669,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>True</t>
@@ -9175,14 +8681,12 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
       </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/5c131128f25048f796ccb3b2a34118ca/detail</t>
@@ -9231,9 +8735,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>True</t>
@@ -9245,14 +8747,12 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
       </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/7b8ce8a8a2a44f1e8ec34bfdb9c2d437/detail</t>
@@ -9301,9 +8801,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>True</t>
@@ -9315,14 +8813,12 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
       </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/86cf7027eb294196b5ba0f0e07b4060b/detail</t>
@@ -9371,9 +8867,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>True</t>
@@ -9385,14 +8879,12 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1227</v>
+        <v>1278</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
       </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/08c33f024bf943ef9b9c028a7d03f228/detail</t>
@@ -9441,9 +8933,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>True</t>
@@ -9455,14 +8945,12 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
       </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/5c415801ddfc47ddb857ecdf1187c630/detail</t>
@@ -9511,9 +8999,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>True</t>
@@ -9525,14 +9011,12 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
       </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/37755611750841079cb2671556dc0dda/detail</t>
@@ -9581,9 +9065,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I131" t="n">
-        <v>0</v>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>True</t>
@@ -9595,14 +9077,12 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1424</v>
+        <v>1459</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
       </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/f3391d194a3a4377b358e547ff27b403/detail</t>
@@ -9651,9 +9131,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>True</t>
@@ -9665,14 +9143,12 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1646</v>
+        <v>1682</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
       </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/a68ba85337154f7ea81efcf5c448b0c4/detail</t>
@@ -9688,22 +9164,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>五莲县矿山审批信息一览表分页查询服务</t>
+          <t>开发区各级教学能手名单分页查询服务</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>资源环境</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>五莲县矿山审批信息一览表分页查询服务</t>
+          <t>开发区各级教学能手名单分页查询服务</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -9721,9 +9197,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>True</t>
@@ -9735,17 +9209,15 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>203</v>
+        <v>138</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/185e336164d5416fb6c018b6a6f2a1de/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/090912c0806d434495947ecc6be09aa1/detail</t>
         </is>
       </c>
       <c r="P133" t="inlineStr"/>
@@ -9758,17 +9230,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>五莲县学科带头人名单分页查询服务</t>
+          <t>五莲县矿山审批信息一览表分页查询服务</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>五莲县学科带头人名单分页查询服务</t>
+          <t>五莲县矿山审批信息一览表分页查询服务</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9791,9 +9263,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>True</t>
@@ -9805,17 +9275,15 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
       </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/187a4f24ade84834a6b2bb50280ec437/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/185e336164d5416fb6c018b6a6f2a1de/detail</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -9828,17 +9296,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>五莲县农村幸福院信息分页查询服务</t>
+          <t>五莲县学科带头人名单分页查询服务</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>五莲县农村幸福院信息分页查询服务</t>
+          <t>五莲县学科带头人名单分页查询服务</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9861,9 +9329,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>True</t>
@@ -9875,17 +9341,15 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
       </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1da8d4b6fdb14927bca6ea2e79d72afe/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/187a4f24ade84834a6b2bb50280ec437/detail</t>
         </is>
       </c>
       <c r="P135" t="inlineStr"/>
@@ -9898,7 +9362,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>五莲县城市低保人员信息分页查询服务</t>
+          <t>五莲县农村幸福院信息分页查询服务</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9908,7 +9372,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>五莲县城市低保人员信息分页查询服务</t>
+          <t>五莲县农村幸福院信息分页查询服务</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9931,9 +9395,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>True</t>
@@ -9945,17 +9407,15 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
       </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/31ad35e16e7f49b6b372e8f925ba31d8/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/1da8d4b6fdb14927bca6ea2e79d72afe/detail</t>
         </is>
       </c>
       <c r="P136" t="inlineStr"/>
@@ -9968,17 +9428,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>五莲县食品生产行政许可信息分页查询服务</t>
+          <t>五莲县城市低保人员信息分页查询服务</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>五莲县食品生产行政许可信息分页查询服务</t>
+          <t>五莲县城市低保人员信息分页查询服务</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -10001,9 +9461,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>True</t>
@@ -10015,17 +9473,15 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
       </c>
-      <c r="N137" t="n">
-        <v>0</v>
-      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/34f44bdaf9234c58b98ef2700a4cbf14/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/31ad35e16e7f49b6b372e8f925ba31d8/detail</t>
         </is>
       </c>
       <c r="P137" t="inlineStr"/>
@@ -10038,17 +9494,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>五莲名师信息分页查询服务</t>
+          <t>五莲县食品生产行政许可信息分页查询服务</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>五莲名师信息分页查询服务</t>
+          <t>五莲县食品生产行政许可信息分页查询服务</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -10071,9 +9527,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>True</t>
@@ -10085,17 +9539,15 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
       </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3d1c6ff8ad8b4c21968aa6195dd04656/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/34f44bdaf9234c58b98ef2700a4cbf14/detail</t>
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
@@ -10108,7 +9560,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>五莲县义务教育学校名单分页查询服务</t>
+          <t>五莲名师信息分页查询服务</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -10118,7 +9570,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>五莲县义务教育学校名单分页查询服务</t>
+          <t>五莲名师信息分页查询服务</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -10141,9 +9593,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>True</t>
@@ -10155,17 +9605,15 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>196</v>
+        <v>105</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
       </c>
-      <c r="N139" t="n">
-        <v>0</v>
-      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/48a8dcba091a468782b7e7f3748d80fd/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/3d1c6ff8ad8b4c21968aa6195dd04656/detail</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -10178,22 +9626,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>开发区基本公共卫生服务项目信息分页查询服务</t>
+          <t>五莲县义务教育学校名单分页查询服务</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>开发区基本公共卫生服务项目信息分页查询服务</t>
+          <t>五莲县义务教育学校名单分页查询服务</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -10211,9 +9659,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>True</t>
@@ -10225,17 +9671,15 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
       </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/4e93ad469d58439a8c44d8d7863f0422/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/48a8dcba091a468782b7e7f3748d80fd/detail</t>
         </is>
       </c>
       <c r="P140" t="inlineStr"/>
@@ -10248,22 +9692,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>五莲县教学新秀名单分页查询服务</t>
+          <t>开发区基本公共卫生服务项目信息分页查询服务</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>五莲县教学新秀名单分页查询服务</t>
+          <t>开发区基本公共卫生服务项目信息分页查询服务</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -10281,9 +9725,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>True</t>
@@ -10295,17 +9737,15 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
       </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/523c47a90dbd46c09eca9a2d9592397b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/4e93ad469d58439a8c44d8d7863f0422/detail</t>
         </is>
       </c>
       <c r="P141" t="inlineStr"/>
@@ -10351,9 +9791,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>True</t>
@@ -10365,14 +9803,12 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
       </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/523c47a90dbd46c09eca9a2d9592397b/detail</t>
@@ -10388,7 +9824,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>日照经济技术开发区涉氨制冷企业名录分页查询服务</t>
+          <t>五莲县法律服务所信息分页查询服务</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -10398,12 +9834,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>日照经济技术开发区涉氨制冷企业名录分页查询服务</t>
+          <t>五莲县法律服务所信息分页查询服务</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -10421,9 +9857,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I143" t="n">
-        <v>0</v>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>True</t>
@@ -10435,17 +9869,15 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
       </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/75c5e6c1ddbb4441ae579090bbaf11f9/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/618fd0d8752e489b921a317c4c85b432/detail</t>
         </is>
       </c>
       <c r="P143" t="inlineStr"/>
@@ -10458,7 +9890,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>五莲县精品采摘园信息分页查询服务</t>
+          <t>五莲县旅行社信息分页查询服务</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10468,7 +9900,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>五莲县精品采摘园信息分页查询服务</t>
+          <t>五莲县旅行社信息分页查询服务</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -10491,9 +9923,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>True</t>
@@ -10505,17 +9935,15 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
       </c>
-      <c r="N144" t="n">
-        <v>0</v>
-      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7baa236ef7a74301978b5923f6507d1f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/6ca96cfc5f1d411d8255a04d8f43e2b6/detail</t>
         </is>
       </c>
       <c r="P144" t="inlineStr"/>
@@ -10528,17 +9956,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>中秋节日市场食品监督抽检产品信息分页查询服务</t>
+          <t>开发区学前教育学校名单分页查询服务</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>中秋节日市场食品监督抽检产品信息分页查询服务</t>
+          <t>开发区学前教育学校名单分页查询服务</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -10561,9 +9989,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I145" t="n">
-        <v>0</v>
-      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>True</t>
@@ -10575,17 +10001,15 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
       </c>
-      <c r="N145" t="n">
-        <v>0</v>
-      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/97996d4b9b874c788b0a30615e203dfe/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/708f807ae4e040edb9a54b870578a4f7/detail</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -10598,22 +10022,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>五莲县特约教育参事名单分页查询服务</t>
+          <t>日照经济技术开发区涉氨制冷企业名录分页查询服务</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>五莲县特约教育参事名单分页查询服务</t>
+          <t>日照经济技术开发区涉氨制冷企业名录分页查询服务</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -10631,9 +10055,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I146" t="n">
-        <v>0</v>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>True</t>
@@ -10645,17 +10067,15 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>91</v>
+        <v>197</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
       </c>
-      <c r="N146" t="n">
-        <v>0</v>
-      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/ce7b5e609e9c4ff7a72c3997110e0416/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/75c5e6c1ddbb4441ae579090bbaf11f9/detail</t>
         </is>
       </c>
       <c r="P146" t="inlineStr"/>
@@ -10668,17 +10088,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>五莲县县乡等级公路路网信息分页查询服务</t>
+          <t>五莲县精品采摘园信息分页查询服务</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>五莲县县乡等级公路路网信息分页查询服务</t>
+          <t>五莲县精品采摘园信息分页查询服务</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -10701,9 +10121,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>True</t>
@@ -10715,17 +10133,15 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
       </c>
-      <c r="N147" t="n">
-        <v>0</v>
-      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/cf569f9a1a874799aabb14c749b92ce4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7baa236ef7a74301978b5923f6507d1f/detail</t>
         </is>
       </c>
       <c r="P147" t="inlineStr"/>
@@ -10738,7 +10154,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>学校食堂食品监督抽检产品信息分页查询服务</t>
+          <t>中秋节日市场食品监督抽检产品信息分页查询服务</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10748,7 +10164,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>学校食堂食品监督抽检产品信息分页查询服务</t>
+          <t>中秋节日市场食品监督抽检产品信息分页查询服务</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -10771,9 +10187,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>True</t>
@@ -10785,17 +10199,15 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
       </c>
-      <c r="N148" t="n">
-        <v>0</v>
-      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/feb93f1f74ba4e74a5d5f4f2223c1e92/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/97996d4b9b874c788b0a30615e203dfe/detail</t>
         </is>
       </c>
       <c r="P148" t="inlineStr"/>
@@ -10808,22 +10220,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>五莲县法律服务所信息分页查询服务</t>
+          <t>开发区各级学科带头人名单分页查询服务</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>五莲县法律服务所信息分页查询服务</t>
+          <t>开发区各级学科带头人名单分页查询服务</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -10841,9 +10253,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I149" t="n">
-        <v>0</v>
-      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>True</t>
@@ -10855,17 +10265,15 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
       </c>
-      <c r="N149" t="n">
-        <v>0</v>
-      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/618fd0d8752e489b921a317c4c85b432/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a16403fcad4e4a5fb6839ffbd2c4dc0a/detail</t>
         </is>
       </c>
       <c r="P149" t="inlineStr"/>
@@ -10878,17 +10286,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>五莲县旅行社信息分页查询服务</t>
+          <t>五莲县特约教育参事名单分页查询服务</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>五莲县旅行社信息分页查询服务</t>
+          <t>五莲县特约教育参事名单分页查询服务</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -10911,9 +10319,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>True</t>
@@ -10925,17 +10331,15 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
       </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/6ca96cfc5f1d411d8255a04d8f43e2b6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/ce7b5e609e9c4ff7a72c3997110e0416/detail</t>
         </is>
       </c>
       <c r="P150" t="inlineStr"/>
@@ -10948,22 +10352,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>开发区学前教育学校名单分页查询服务</t>
+          <t>五莲县县乡等级公路路网信息分页查询服务</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>开发区学前教育学校名单分页查询服务</t>
+          <t>五莲县县乡等级公路路网信息分页查询服务</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -10981,9 +10385,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>True</t>
@@ -10995,17 +10397,15 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
       </c>
-      <c r="N151" t="n">
-        <v>0</v>
-      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/708f807ae4e040edb9a54b870578a4f7/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/cf569f9a1a874799aabb14c749b92ce4/detail</t>
         </is>
       </c>
       <c r="P151" t="inlineStr"/>
@@ -11051,9 +10451,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>True</t>
@@ -11065,14 +10463,12 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
       </c>
-      <c r="N152" t="n">
-        <v>0</v>
-      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/feb93f1f74ba4e74a5d5f4f2223c1e92/detail</t>
@@ -11088,22 +10484,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>开发区执业医师注册信息分页查询服务</t>
+          <t>东港区校园足球特色学校名单分页查询服务</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>开发区执业医师注册信息分页查询服务</t>
+          <t>东港区校园足球特色学校名单分页查询服务</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市东港区</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -11121,9 +10517,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>True</t>
@@ -11135,17 +10529,15 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>44</v>
+        <v>512</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
       </c>
-      <c r="N153" t="n">
-        <v>0</v>
-      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/06f460a8e41840dba8df052b02f68407/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/48b668b3d7894077b8d394375ecb928f/detail</t>
         </is>
       </c>
       <c r="P153" t="inlineStr"/>
@@ -11158,22 +10550,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>五莲县食品经营企业信息分页查询服务</t>
+          <t>开发区农村低保家庭信息分页查询服务</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>五莲县食品经营企业信息分页查询服务</t>
+          <t>开发区农村低保家庭信息分页查询服务</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -11191,9 +10583,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I154" t="n">
-        <v>0</v>
-      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>True</t>
@@ -11205,17 +10595,15 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
       </c>
-      <c r="N154" t="n">
-        <v>0</v>
-      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/0fe18269d0134c4685576508800618fd/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/49ce58a7fd614f2f87b98ddab4e930e0/detail</t>
         </is>
       </c>
       <c r="P154" t="inlineStr"/>
@@ -11228,17 +10616,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>五莲县综合行政执法局行政处罚信息分页查询服务</t>
+          <t>五莲县学前教育学校名单分页查询服务</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>五莲县综合行政执法局行政处罚信息分页查询服务</t>
+          <t>五莲县学前教育学校名单分页查询服务</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -11261,9 +10649,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>True</t>
@@ -11275,17 +10661,15 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
       </c>
-      <c r="N155" t="n">
-        <v>0</v>
-      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/6e07ef9aa1aa4b76bcb858022dd5aee8/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/76e68c2a99aa479b897cf3479de538d4/detail</t>
         </is>
       </c>
       <c r="P155" t="inlineStr"/>
@@ -11298,17 +10682,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>五莲县学前教育学校名单分页查询服务</t>
+          <t>五莲县社区卫生服务中心和卫生院国医堂信息分页查询服务</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>五莲县学前教育学校名单分页查询服务</t>
+          <t>五莲县社区卫生服务中心和卫生院国医堂信息分页查询服务</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -11331,9 +10715,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I156" t="n">
-        <v>0</v>
-      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>True</t>
@@ -11345,17 +10727,15 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
       </c>
-      <c r="N156" t="n">
-        <v>0</v>
-      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/76e68c2a99aa479b897cf3479de538d4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/781262d3606148179f7cd24adafff42b/detail</t>
         </is>
       </c>
       <c r="P156" t="inlineStr"/>
@@ -11368,17 +10748,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>五莲县社区卫生服务中心和卫生院国医堂信息分页查询服务</t>
+          <t>五莲县城区公交线路站点时间信息分页查询服务</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>五莲县社区卫生服务中心和卫生院国医堂信息分页查询服务</t>
+          <t>五莲县城区公交线路站点时间信息分页查询服务</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -11401,9 +10781,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I157" t="n">
-        <v>0</v>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>True</t>
@@ -11415,17 +10793,15 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
       </c>
-      <c r="N157" t="n">
-        <v>0</v>
-      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/781262d3606148179f7cd24adafff42b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/8089724f84b6420382f93216c23f9db5/detail</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -11438,17 +10814,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>五莲县城区公交线路站点时间信息分页查询服务</t>
+          <t>五莲县五保人员信息分页查询服务</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>五莲县城区公交线路站点时间信息分页查询服务</t>
+          <t>五莲县五保人员信息分页查询服务</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -11471,9 +10847,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>True</t>
@@ -11485,17 +10859,15 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
       </c>
-      <c r="N158" t="n">
-        <v>0</v>
-      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/8089724f84b6420382f93216c23f9db5/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/810e8a7dc54e43e38048651122da52af/detail</t>
         </is>
       </c>
       <c r="P158" t="inlineStr"/>
@@ -11508,22 +10880,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>五莲县五保人员信息分页查询服务</t>
+          <t>东港区最美乡村教师名单分页查询服务</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>五莲县五保人员信息分页查询服务</t>
+          <t>东港区最美乡村教师名单分页查询服务</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市东港区</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -11541,9 +10913,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I159" t="n">
-        <v>0</v>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>True</t>
@@ -11555,17 +10925,15 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>32</v>
+        <v>869</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
       </c>
-      <c r="N159" t="n">
-        <v>0</v>
-      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/810e8a7dc54e43e38048651122da52af/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/84e5d7bbdd8a4259b9365ff31092aff3/detail</t>
         </is>
       </c>
       <c r="P159" t="inlineStr"/>
@@ -11578,22 +10946,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>东港区最美乡村教师名单分页查询服务</t>
+          <t>三小环节食品监督抽检产品信息分页查询服务</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>东港区最美乡村教师名单分页查询服务</t>
+          <t>三小环节食品监督抽检产品信息分页查询服务</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>日照市东港区</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -11611,9 +10979,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>True</t>
@@ -11625,17 +10991,15 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>862</v>
+        <v>27</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
       </c>
-      <c r="N160" t="n">
-        <v>0</v>
-      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/84e5d7bbdd8a4259b9365ff31092aff3/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/94970016e0dc4e66ae94b4893dd6064c/detail</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -11648,17 +11012,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>五莲县出租车信息分页查询服务</t>
+          <t>五莲县各乡镇（街道）司法所信息分页查询服务</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>五莲县出租车信息分页查询服务</t>
+          <t>五莲县各乡镇（街道）司法所信息分页查询服务</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -11681,9 +11045,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>True</t>
@@ -11695,17 +11057,15 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
       </c>
-      <c r="N161" t="n">
-        <v>0</v>
-      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/c1b852ec691c437e8a323143642bd4e4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b15e9af6556346419a6042369058c407/detail</t>
         </is>
       </c>
       <c r="P161" t="inlineStr"/>
@@ -11718,17 +11078,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>五莲县出租车信息分页查询服务</t>
+          <t>五莲县综合行政执法局行政处罚信息分页查询服务</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>五莲县出租车信息分页查询服务</t>
+          <t>五莲县综合行政执法局行政处罚信息分页查询服务</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -11751,9 +11111,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I162" t="n">
-        <v>0</v>
-      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>True</t>
@@ -11765,17 +11123,15 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
       </c>
-      <c r="N162" t="n">
-        <v>0</v>
-      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/c1b852ec691c437e8a323143642bd4e4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/6e07ef9aa1aa4b76bcb858022dd5aee8/detail</t>
         </is>
       </c>
       <c r="P162" t="inlineStr"/>
@@ -11788,17 +11144,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>五莲县城镇在岗职工年平均工资分页查询服务</t>
+          <t>五莲县学前教育学校名单分页查询服务</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>五莲县城镇在岗职工年平均工资分页查询服务</t>
+          <t>五莲县学前教育学校名单分页查询服务</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -11821,9 +11177,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>True</t>
@@ -11835,17 +11189,15 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
       </c>
-      <c r="N163" t="n">
-        <v>0</v>
-      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/c4315d03a7a2402f973ee3e0625cf02d/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/76e68c2a99aa479b897cf3479de538d4/detail</t>
         </is>
       </c>
       <c r="P163" t="inlineStr"/>
@@ -11858,17 +11210,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>五莲县各乡镇（街道）司法所信息分页查询服务</t>
+          <t>五莲县社区卫生服务中心和卫生院国医堂信息分页查询服务</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>五莲县各乡镇（街道）司法所信息分页查询服务</t>
+          <t>五莲县社区卫生服务中心和卫生院国医堂信息分页查询服务</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -11891,9 +11243,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I164" t="n">
-        <v>0</v>
-      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>True</t>
@@ -11905,17 +11255,15 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
       </c>
-      <c r="N164" t="n">
-        <v>0</v>
-      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b15e9af6556346419a6042369058c407/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/781262d3606148179f7cd24adafff42b/detail</t>
         </is>
       </c>
       <c r="P164" t="inlineStr"/>
@@ -11928,22 +11276,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>东港区最美乡村教师名单分页查询服务</t>
+          <t>五莲县城区公交线路站点时间信息分页查询服务</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>东港区最美乡村教师名单分页查询服务</t>
+          <t>五莲县城区公交线路站点时间信息分页查询服务</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>日照市东港区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -11961,9 +11309,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I165" t="n">
-        <v>0</v>
-      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>True</t>
@@ -11975,17 +11321,15 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>862</v>
+        <v>103</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
       </c>
-      <c r="N165" t="n">
-        <v>0</v>
-      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/84e5d7bbdd8a4259b9365ff31092aff3/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/8089724f84b6420382f93216c23f9db5/detail</t>
         </is>
       </c>
       <c r="P165" t="inlineStr"/>
@@ -11998,22 +11342,22 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>三小环节食品监督抽检产品信息分页查询服务</t>
+          <t>五莲县五保人员信息分页查询服务</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>三小环节食品监督抽检产品信息分页查询服务</t>
+          <t>五莲县五保人员信息分页查询服务</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -12031,9 +11375,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>True</t>
@@ -12045,17 +11387,15 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
       </c>
-      <c r="N166" t="n">
-        <v>0</v>
-      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/94970016e0dc4e66ae94b4893dd6064c/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/810e8a7dc54e43e38048651122da52af/detail</t>
         </is>
       </c>
       <c r="P166" t="inlineStr"/>
@@ -12068,22 +11408,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>五莲县危险货物运输经营以外的道路货运运输经营许可信息分页查询服务</t>
+          <t>东港区最美乡村教师名单分页查询服务</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>五莲县危险货物运输经营以外的道路货运运输经营许可信息分页查询服务</t>
+          <t>东港区最美乡村教师名单分页查询服务</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市东港区</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -12101,9 +11441,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I167" t="n">
-        <v>0</v>
-      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>True</t>
@@ -12115,17 +11453,15 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>88</v>
+        <v>869</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
       </c>
-      <c r="N167" t="n">
-        <v>0</v>
-      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/56a944d6fd6a4a73838844004fc8a66d/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/84e5d7bbdd8a4259b9365ff31092aff3/detail</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -12138,22 +11474,22 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>五莲县就业扶贫车间名录分页查询服务</t>
+          <t>三小环节食品监督抽检产品信息分页查询服务</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>五莲县就业扶贫车间名录分页查询服务</t>
+          <t>三小环节食品监督抽检产品信息分页查询服务</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -12171,9 +11507,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>True</t>
@@ -12185,17 +11519,15 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
       </c>
-      <c r="N168" t="n">
-        <v>0</v>
-      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5b6fcea58d4a45a8b190c53fdf1ed816/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/94970016e0dc4e66ae94b4893dd6064c/detail</t>
         </is>
       </c>
       <c r="P168" t="inlineStr"/>
@@ -12208,22 +11540,22 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>开发区危险货物运输经营以外的道路货运运输经营许可信息分页查询服务</t>
+          <t>五莲县各乡镇（街道）司法所信息分页查询服务</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>开发区危险货物运输经营以外的道路货运运输经营许可信息分页查询服务</t>
+          <t>五莲县各乡镇（街道）司法所信息分页查询服务</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -12241,9 +11573,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>0</v>
-      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>True</t>
@@ -12255,17 +11585,15 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="M169" t="n">
         <v>0</v>
       </c>
-      <c r="N169" t="n">
-        <v>0</v>
-      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5bba86b223384e0ead9b6cbcf35a5f18/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b15e9af6556346419a6042369058c407/detail</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -12278,22 +11606,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>开发区城市低保人员信息分页查询服务</t>
+          <t>五莲县城区免费开放公园广场信息分页查询服务</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>开发区城市低保人员信息分页查询服务</t>
+          <t>五莲县城区免费开放公园广场信息分页查询服务</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -12311,9 +11639,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I170" t="n">
-        <v>0</v>
-      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>True</t>
@@ -12325,17 +11651,15 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
       </c>
-      <c r="N170" t="n">
-        <v>0</v>
-      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5edf556ace2140cfaf34c1ae120d99bc/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b9708894e33b448ea5630aaba59d6b86/detail</t>
         </is>
       </c>
       <c r="P170" t="inlineStr"/>
@@ -12348,17 +11672,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>五莲县历年总人口分页查询服务</t>
+          <t>五莲县出租车信息分页查询服务</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>五莲县历年总人口分页查询服务</t>
+          <t>五莲县出租车信息分页查询服务</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -12381,9 +11705,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I171" t="n">
-        <v>0</v>
-      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>True</t>
@@ -12395,17 +11717,15 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
       </c>
-      <c r="N171" t="n">
-        <v>0</v>
-      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5fa21801c006400fbeb052c15f11ffa6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/c1b852ec691c437e8a323143642bd4e4/detail</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -12418,7 +11738,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>开发区危险货物运输经营以外的道路货运运输经营许可信息分页查询服务</t>
+          <t>五莲县出租车信息分页查询服务</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -12428,12 +11748,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>开发区危险货物运输经营以外的道路货运运输经营许可信息分页查询服务</t>
+          <t>五莲县出租车信息分页查询服务</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -12451,9 +11771,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I172" t="n">
-        <v>0</v>
-      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>True</t>
@@ -12465,17 +11783,15 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="M172" t="n">
         <v>0</v>
       </c>
-      <c r="N172" t="n">
-        <v>0</v>
-      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5bba86b223384e0ead9b6cbcf35a5f18/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/c1b852ec691c437e8a323143642bd4e4/detail</t>
         </is>
       </c>
       <c r="P172" t="inlineStr"/>
@@ -12488,22 +11804,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>开发区城市低保人员信息分页查询服务</t>
+          <t>五莲县城镇在岗职工年平均工资分页查询服务</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>开发区城市低保人员信息分页查询服务</t>
+          <t>五莲县城镇在岗职工年平均工资分页查询服务</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -12521,9 +11837,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I173" t="n">
-        <v>0</v>
-      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>True</t>
@@ -12535,17 +11849,15 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="M173" t="n">
         <v>0</v>
       </c>
-      <c r="N173" t="n">
-        <v>0</v>
-      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5edf556ace2140cfaf34c1ae120d99bc/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/c4315d03a7a2402f973ee3e0625cf02d/detail</t>
         </is>
       </c>
       <c r="P173" t="inlineStr"/>
@@ -12558,17 +11870,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>五莲县历年总人口分页查询服务</t>
+          <t>五莲县公共场所卫生许可信息分页查询服务</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>五莲县历年总人口分页查询服务</t>
+          <t>五莲县公共场所卫生许可信息分页查询服务</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -12591,9 +11903,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I174" t="n">
-        <v>0</v>
-      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>True</t>
@@ -12605,17 +11915,15 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
       </c>
-      <c r="N174" t="n">
-        <v>0</v>
-      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5fa21801c006400fbeb052c15f11ffa6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d991a9cd05d84d598b3240c4a87e7625/detail</t>
         </is>
       </c>
       <c r="P174" t="inlineStr"/>
@@ -12628,22 +11936,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>动物诊疗机构名单信息分页查询服务</t>
+          <t>开发区特困人员信息分页查询服务</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>动物诊疗机构名单信息分页查询服务</t>
+          <t>开发区特困人员信息分页查询服务</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>日照市东港区</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -12661,9 +11969,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I175" t="n">
-        <v>0</v>
-      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>True</t>
@@ -12675,17 +11981,15 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>935</v>
+        <v>127</v>
       </c>
       <c r="M175" t="n">
         <v>0</v>
       </c>
-      <c r="N175" t="n">
-        <v>0</v>
-      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/09f61d4848804f779a0d76eda49b2cca/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/03b5f6d8645d4b3ab8064ba8d68c2a87/detail</t>
         </is>
       </c>
       <c r="P175" t="inlineStr"/>
@@ -12698,22 +12002,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>五莲县市级一类幼儿园名单分页查询服务</t>
+          <t>动物诊疗机构名单信息分页查询服务</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>五莲县市级一类幼儿园名单分页查询服务</t>
+          <t>动物诊疗机构名单信息分页查询服务</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市东港区</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -12731,9 +12035,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I176" t="n">
-        <v>0</v>
-      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>True</t>
@@ -12745,17 +12047,15 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>40</v>
+        <v>940</v>
       </c>
       <c r="M176" t="n">
         <v>0</v>
       </c>
-      <c r="N176" t="n">
-        <v>0</v>
-      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/0a4573732d45455b8bcccfaff6091256/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/09f61d4848804f779a0d76eda49b2cca/detail</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -12768,17 +12068,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>五莲县学校体育教师裁判员等级信息分页查询服务</t>
+          <t>五莲县市级一类幼儿园名单分页查询服务</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>五莲县学校体育教师裁判员等级信息分页查询服务</t>
+          <t>五莲县市级一类幼儿园名单分页查询服务</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -12801,9 +12101,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I177" t="n">
-        <v>0</v>
-      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>True</t>
@@ -12815,17 +12113,15 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
       </c>
-      <c r="N177" t="n">
-        <v>0</v>
-      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/19b8948c897e431b8fba3da2a3636bca/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/0a4573732d45455b8bcccfaff6091256/detail</t>
         </is>
       </c>
       <c r="P177" t="inlineStr"/>
@@ -12838,17 +12134,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>五莲县道路运输从业人员、危险货物运输从业人员从业资格证信息分页查询服务</t>
+          <t>五莲县学校体育教师裁判员等级信息分页查询服务</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>五莲县道路运输从业人员、危险货物运输从业人员从业资格证信息分页查询服务</t>
+          <t>五莲县学校体育教师裁判员等级信息分页查询服务</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -12871,9 +12167,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I178" t="n">
-        <v>0</v>
-      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>True</t>
@@ -12885,17 +12179,15 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="M178" t="n">
         <v>0</v>
       </c>
-      <c r="N178" t="n">
-        <v>0</v>
-      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/274cb4713a744e85b43ae90a6754031b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/19b8948c897e431b8fba3da2a3636bca/detail</t>
         </is>
       </c>
       <c r="P178" t="inlineStr"/>
@@ -12908,17 +12200,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>五莲县历年固定资产投资分页查询服务</t>
+          <t>五莲县道路运输从业人员、危险货物运输从业人员从业资格证信息分页查询服务</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>五莲县历年固定资产投资分页查询服务</t>
+          <t>五莲县道路运输从业人员、危险货物运输从业人员从业资格证信息分页查询服务</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -12941,9 +12233,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I179" t="n">
-        <v>0</v>
-      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>True</t>
@@ -12955,17 +12245,15 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>
       </c>
-      <c r="N179" t="n">
-        <v>0</v>
-      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2871ba4e556d44f2b2ff751be16d0473/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/274cb4713a744e85b43ae90a6754031b/detail</t>
         </is>
       </c>
       <c r="P179" t="inlineStr"/>
@@ -12978,22 +12266,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>开发区特困人员信息分页查询服务</t>
+          <t>五莲县历年固定资产投资分页查询服务</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>开发区特困人员信息分页查询服务</t>
+          <t>五莲县历年固定资产投资分页查询服务</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -13011,9 +12299,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I180" t="n">
-        <v>0</v>
-      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>True</t>
@@ -13025,17 +12311,15 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="M180" t="n">
         <v>0</v>
       </c>
-      <c r="N180" t="n">
-        <v>0</v>
-      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/03b5f6d8645d4b3ab8064ba8d68c2a87/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2871ba4e556d44f2b2ff751be16d0473/detail</t>
         </is>
       </c>
       <c r="P180" t="inlineStr"/>
@@ -13048,17 +12332,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>五莲县非物质文化遗产名录分页查询服务</t>
+          <t>五莲县机动车维修经营许可信息分页查询服务</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>交通出行</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>五莲县非物质文化遗产名录分页查询服务</t>
+          <t>五莲县机动车维修经营许可信息分页查询服务</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -13081,9 +12365,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I181" t="n">
-        <v>0</v>
-      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>True</t>
@@ -13095,17 +12377,15 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
       </c>
-      <c r="N181" t="n">
-        <v>0</v>
-      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d5eca7a2c40d4710b2bb8673b24a640d/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2f203c8fdc4e4da1ab58e7ee3a4730d6/detail</t>
         </is>
       </c>
       <c r="P181" t="inlineStr"/>
@@ -13118,22 +12398,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>五莲县机动车维修经营许可信息分页查询服务</t>
+          <t>春节节日市场食品监督抽检产品信息分页查询服务</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>五莲县机动车维修经营许可信息分页查询服务</t>
+          <t>春节节日市场食品监督抽检产品信息分页查询服务</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -13151,9 +12431,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I182" t="n">
-        <v>0</v>
-      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>True</t>
@@ -13165,17 +12443,15 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="M182" t="n">
         <v>0</v>
       </c>
-      <c r="N182" t="n">
-        <v>0</v>
-      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2f203c8fdc4e4da1ab58e7ee3a4730d6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/54c58f361e804d9e8a4dda6527a02dc1/detail</t>
         </is>
       </c>
       <c r="P182" t="inlineStr"/>
@@ -13188,7 +12464,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>五莲县在营农民合作社基本信息分页查询服务</t>
+          <t>五莲县危险化学品经营企业（加油站）分页查询服务</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -13198,7 +12474,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>五莲县在营农民合作社基本信息分页查询服务</t>
+          <t>五莲县危险化学品经营企业（加油站）分页查询服务</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -13221,9 +12497,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I183" t="n">
-        <v>0</v>
-      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>True</t>
@@ -13235,17 +12509,15 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
       </c>
-      <c r="N183" t="n">
-        <v>0</v>
-      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b13f4b1d8c6a469eb852d16517d759f6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/886de1b2a5d84f3eb143aaec2efce6a0/detail</t>
         </is>
       </c>
       <c r="P183" t="inlineStr"/>
@@ -13258,17 +12530,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>五莲县残疾人两项补贴分页查询服务</t>
+          <t>五莲县历年社会消费品零售总额分页查询服务</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>五莲县残疾人两项补贴分页查询服务</t>
+          <t>五莲县历年社会消费品零售总额分页查询服务</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -13291,9 +12563,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I184" t="n">
-        <v>0</v>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>True</t>
@@ -13305,17 +12575,15 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="M184" t="n">
         <v>0</v>
       </c>
-      <c r="N184" t="n">
-        <v>0</v>
-      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b395f0e8471d4fa0ad8540ab9a0e9ebc/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9595b981d3064c79884e0495a9698d41/detail</t>
         </is>
       </c>
       <c r="P184" t="inlineStr"/>
@@ -13328,22 +12596,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>五莲县农民健身工程信息分页查询服务</t>
+          <t>日照经济技术开发区危险化学品经营企业（危化品无储存经营企业）分页查询服务</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>五莲县农民健身工程信息分页查询服务</t>
+          <t>日照经济技术开发区危险化学品经营企业（危化品无储存经营企业）分页查询服务</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -13361,9 +12629,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I185" t="n">
-        <v>0</v>
-      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>True</t>
@@ -13375,17 +12641,15 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="M185" t="n">
         <v>0</v>
       </c>
-      <c r="N185" t="n">
-        <v>0</v>
-      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/cb2f9da9e09549ec9cc197dabfbeaee8/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/97b72945cba244c0a4326d3310eb07cb/detail</t>
         </is>
       </c>
       <c r="P185" t="inlineStr"/>
@@ -13398,22 +12662,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>五莲县危险化学品经营企业（加油站）分页查询服务</t>
+          <t>开发区各级教学新秀名单分页查询服务</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>五莲县危险化学品经营企业（加油站）分页查询服务</t>
+          <t>开发区各级教学新秀名单分页查询服务</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -13431,9 +12695,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I186" t="n">
-        <v>0</v>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>True</t>
@@ -13445,17 +12707,15 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="M186" t="n">
         <v>0</v>
       </c>
-      <c r="N186" t="n">
-        <v>0</v>
-      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/886de1b2a5d84f3eb143aaec2efce6a0/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a0c7116211d14330bea63a46a164b6f4/detail</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -13468,17 +12728,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>五莲县历年社会消费品零售总额分页查询服务</t>
+          <t>五莲县高中教学工作先进个人名单分页查询服务</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>五莲县历年社会消费品零售总额分页查询服务</t>
+          <t>五莲县高中教学工作先进个人名单分页查询服务</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -13501,9 +12761,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I187" t="n">
-        <v>0</v>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>True</t>
@@ -13515,17 +12773,15 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="M187" t="n">
         <v>0</v>
       </c>
-      <c r="N187" t="n">
-        <v>0</v>
-      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9595b981d3064c79884e0495a9698d41/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a4128c3365874d32a389e9526a82bc6f/detail</t>
         </is>
       </c>
       <c r="P187" t="inlineStr"/>
@@ -13538,7 +12794,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>日照经济技术开发区危险化学品经营企业（危化品无储存经营企业）分页查询服务</t>
+          <t>开发区食品经营企业信息分页查询服务</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -13548,7 +12804,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>日照经济技术开发区危险化学品经营企业（危化品无储存经营企业）分页查询服务</t>
+          <t>开发区食品经营企业信息分页查询服务</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -13571,9 +12827,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I188" t="n">
-        <v>0</v>
-      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>True</t>
@@ -13585,17 +12839,15 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="M188" t="n">
         <v>0</v>
       </c>
-      <c r="N188" t="n">
-        <v>0</v>
-      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/97b72945cba244c0a4326d3310eb07cb/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/aaa5524747a94f649ffb08be24063757/detail</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -13608,22 +12860,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>开发区各级教学新秀名单分页查询服务</t>
+          <t>五莲县在营农民合作社基本信息分页查询服务</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>文化休闲</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>开发区各级教学新秀名单分页查询服务</t>
+          <t>五莲县在营农民合作社基本信息分页查询服务</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -13641,9 +12893,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I189" t="n">
-        <v>0</v>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>True</t>
@@ -13655,17 +12905,15 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
       </c>
-      <c r="N189" t="n">
-        <v>0</v>
-      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a0c7116211d14330bea63a46a164b6f4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b13f4b1d8c6a469eb852d16517d759f6/detail</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -13678,17 +12926,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>五莲县高中教学工作先进个人名单分页查询服务</t>
+          <t>五莲县残疾人两项补贴分页查询服务</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>五莲县高中教学工作先进个人名单分页查询服务</t>
+          <t>五莲县残疾人两项补贴分页查询服务</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -13711,9 +12959,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I190" t="n">
-        <v>0</v>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>True</t>
@@ -13725,17 +12971,15 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="M190" t="n">
         <v>0</v>
       </c>
-      <c r="N190" t="n">
-        <v>0</v>
-      </c>
+      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a4128c3365874d32a389e9526a82bc6f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b395f0e8471d4fa0ad8540ab9a0e9ebc/detail</t>
         </is>
       </c>
       <c r="P190" t="inlineStr"/>
@@ -13748,22 +12992,22 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>开发区食品经营企业信息分页查询服务</t>
+          <t>五莲县农民健身工程信息分页查询服务</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>文化休闲</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>开发区食品经营企业信息分页查询服务</t>
+          <t>五莲县农民健身工程信息分页查询服务</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>日照市经济技术开发区</t>
+          <t>日照市五莲县</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -13781,9 +13025,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I191" t="n">
-        <v>0</v>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>True</t>
@@ -13795,17 +13037,15 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="M191" t="n">
         <v>0</v>
       </c>
-      <c r="N191" t="n">
-        <v>0</v>
-      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/aaa5524747a94f649ffb08be24063757/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/cb2f9da9e09549ec9cc197dabfbeaee8/detail</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
@@ -13818,7 +13058,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>五莲县学校体育教师裁判员等级信息分页查询服务</t>
+          <t>五莲县非物质文化遗产名录分页查询服务</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -13828,7 +13068,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>五莲县学校体育教师裁判员等级信息分页查询服务</t>
+          <t>五莲县非物质文化遗产名录分页查询服务</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -13851,9 +13091,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I192" t="n">
-        <v>0</v>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>True</t>
@@ -13865,17 +13103,15 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="M192" t="n">
         <v>0</v>
       </c>
-      <c r="N192" t="n">
-        <v>0</v>
-      </c>
+      <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/19b8948c897e431b8fba3da2a3636bca/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d5eca7a2c40d4710b2bb8673b24a640d/detail</t>
         </is>
       </c>
       <c r="P192" t="inlineStr"/>
@@ -13888,17 +13124,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>五莲县道路运输从业人员、危险货物运输从业人员从业资格证信息分页查询服务</t>
+          <t>五莲县卫计局行政处罚信息分页查询服务</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>五莲县道路运输从业人员、危险货物运输从业人员从业资格证信息分页查询服务</t>
+          <t>五莲县卫计局行政处罚信息分页查询服务</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -13921,9 +13157,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I193" t="n">
-        <v>0</v>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>True</t>
@@ -13935,17 +13169,15 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
       </c>
-      <c r="N193" t="n">
-        <v>0</v>
-      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/274cb4713a744e85b43ae90a6754031b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/fa7da72c5beb43fb8357f0f6cdc37884/detail</t>
         </is>
       </c>
       <c r="P193" t="inlineStr"/>
@@ -13958,22 +13190,22 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>五莲县历年固定资产投资分页查询服务</t>
+          <t>开发区建筑企业登记信息分页查询服务</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>五莲县历年固定资产投资分页查询服务</t>
+          <t>开发区建筑企业登记信息分页查询服务</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -13991,9 +13223,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I194" t="n">
-        <v>0</v>
-      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>True</t>
@@ -14005,17 +13235,15 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="M194" t="n">
         <v>0</v>
       </c>
-      <c r="N194" t="n">
-        <v>0</v>
-      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2871ba4e556d44f2b2ff751be16d0473/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/faae993ee83e4adb9d2095da8acebcfa/detail</t>
         </is>
       </c>
       <c r="P194" t="inlineStr"/>
@@ -14028,22 +13256,22 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>五莲县机动车维修经营许可信息分页查询服务</t>
+          <t>开发区食品生产行政许可信息分页查询服务</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>交通出行</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>五莲县机动车维修经营许可信息分页查询服务</t>
+          <t>开发区食品生产行政许可信息分页查询服务</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>日照市五莲县</t>
+          <t>日照市经济技术开发区</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -14061,9 +13289,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I195" t="n">
-        <v>0</v>
-      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>True</t>
@@ -14075,17 +13301,15 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
       </c>
-      <c r="N195" t="n">
-        <v>0</v>
-      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2f203c8fdc4e4da1ab58e7ee3a4730d6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/fc81abaddc8e4685a62ee1b2bf56dc39/detail</t>
         </is>
       </c>
       <c r="P195" t="inlineStr"/>
@@ -14098,7 +13322,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>日照市拍卖企业名单分页查询服务</t>
+          <t>日照市壹级企业信息分页查询服务</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -14108,17 +13332,17 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>日照市拍卖企业名单分页查询服务</t>
+          <t>日照市壹级企业信息分页查询服务</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>日照市商务局</t>
+          <t>日照市住房和城乡建设局</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2020-03-20</t>
+          <t>2020-03-27</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14131,9 +13355,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I196" t="n">
-        <v>0</v>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>True</t>
@@ -14145,17 +13367,15 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>90</v>
+        <v>5264</v>
       </c>
       <c r="M196" t="n">
         <v>0</v>
       </c>
-      <c r="N196" t="n">
-        <v>0</v>
-      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/18634887d155444096987a6278fc6871/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/0282c396318842d3b4912ce2290df79c/detail</t>
         </is>
       </c>
       <c r="P196" t="inlineStr"/>
@@ -14168,22 +13388,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>山东省服务名信息分页查询服务</t>
+          <t>日照市拍卖企业名单分页查询服务</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>山东省服务名信息分页查询服务</t>
+          <t>日照市拍卖企业名单分页查询服务</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>日照市市场监督管理局</t>
+          <t>日照市商务局</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -14201,9 +13421,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I197" t="n">
-        <v>0</v>
-      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>True</t>
@@ -14215,17 +13433,15 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1434</v>
+        <v>92</v>
       </c>
       <c r="M197" t="n">
         <v>0</v>
       </c>
-      <c r="N197" t="n">
-        <v>0</v>
-      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1a096d7726374fac807c7d15a9ec4be6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/18634887d155444096987a6278fc6871/detail</t>
         </is>
       </c>
       <c r="P197" t="inlineStr"/>
@@ -14238,22 +13454,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>日照市历年城镇化率分页查询服务</t>
+          <t>山东省服务名信息分页查询服务</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>日照市历年城镇化率分页查询服务</t>
+          <t>山东省服务名信息分页查询服务</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市市场监督管理局</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -14271,9 +13487,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I198" t="n">
-        <v>0</v>
-      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>True</t>
@@ -14285,17 +13499,15 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>54</v>
+        <v>1470</v>
       </c>
       <c r="M198" t="n">
         <v>0</v>
       </c>
-      <c r="N198" t="n">
-        <v>0</v>
-      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/21b23577d08a42209fe3f36ed5640ee6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/1a096d7726374fac807c7d15a9ec4be6/detail</t>
         </is>
       </c>
       <c r="P198" t="inlineStr"/>
@@ -14308,22 +13520,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>流通领域成品油和车用尿素质量抽检结果公示信息分页查询服务</t>
+          <t>日照市历年城镇化率分页查询服务</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>流通领域成品油和车用尿素质量抽检结果公示信息分页查询服务</t>
+          <t>日照市历年城镇化率分页查询服务</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>日照市市场监督管理局</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -14341,9 +13553,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I199" t="n">
-        <v>0</v>
-      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>True</t>
@@ -14355,17 +13565,15 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1809</v>
+        <v>55</v>
       </c>
       <c r="M199" t="n">
         <v>0</v>
       </c>
-      <c r="N199" t="n">
-        <v>0</v>
-      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/284c1f0ef1f84ccdbe5b5dd06e1ff7e7/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/21b23577d08a42209fe3f36ed5640ee6/detail</t>
         </is>
       </c>
       <c r="P199" t="inlineStr"/>
@@ -14378,22 +13586,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>日照市历年工业生产者购进价格指数分页查询服务</t>
+          <t>流通领域成品油和车用尿素质量抽检结果公示信息分页查询服务</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>日照市历年工业生产者购进价格指数分页查询服务</t>
+          <t>流通领域成品油和车用尿素质量抽检结果公示信息分页查询服务</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市市场监督管理局</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -14411,9 +13619,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I200" t="n">
-        <v>0</v>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>True</t>
@@ -14425,17 +13631,15 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>31</v>
+        <v>1846</v>
       </c>
       <c r="M200" t="n">
         <v>0</v>
       </c>
-      <c r="N200" t="n">
-        <v>0</v>
-      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2873b95727c94daa90ba85034e850768/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/284c1f0ef1f84ccdbe5b5dd06e1ff7e7/detail</t>
         </is>
       </c>
       <c r="P200" t="inlineStr"/>
@@ -14448,22 +13652,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>医保定点药店分页查询服务</t>
+          <t>日照市历年工业生产者购进价格指数分页查询服务</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>医保定点药店分页查询服务</t>
+          <t>日照市历年工业生产者购进价格指数分页查询服务</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>日照市医疗保障局</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -14481,9 +13685,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I201" t="n">
-        <v>0</v>
-      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>True</t>
@@ -14495,17 +13697,15 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>2303</v>
+        <v>32</v>
       </c>
       <c r="M201" t="n">
         <v>0</v>
       </c>
-      <c r="N201" t="n">
-        <v>0</v>
-      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/329d27482db4428cbe2b70aa24f0783e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2873b95727c94daa90ba85034e850768/detail</t>
         </is>
       </c>
       <c r="P201" t="inlineStr"/>
@@ -14518,22 +13718,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>日照市历年工业总产值分页查询服务</t>
+          <t>医保定点药店分页查询服务</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>日照市历年工业总产值分页查询服务</t>
+          <t>医保定点药店分页查询服务</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市医疗保障局</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -14551,9 +13751,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I202" t="n">
-        <v>0</v>
-      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>True</t>
@@ -14565,17 +13763,15 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>66</v>
+        <v>2323</v>
       </c>
       <c r="M202" t="n">
         <v>0</v>
       </c>
-      <c r="N202" t="n">
-        <v>0</v>
-      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5b92ded873db47a283d59e744b661a0e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/329d27482db4428cbe2b70aa24f0783e/detail</t>
         </is>
       </c>
       <c r="P202" t="inlineStr"/>
@@ -14588,27 +13784,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>日照市壹级企业信息分页查询服务</t>
+          <t>日照市历年工业总产值分页查询服务</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>日照市壹级企业信息分页查询服务</t>
+          <t>日照市历年工业总产值分页查询服务</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>日照市住房和城乡建设局</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2020-03-27</t>
+          <t>2020-03-20</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -14621,9 +13817,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I203" t="n">
-        <v>0</v>
-      </c>
+      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>True</t>
@@ -14635,17 +13829,15 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>5257</v>
+        <v>67</v>
       </c>
       <c r="M203" t="n">
         <v>0</v>
       </c>
-      <c r="N203" t="n">
-        <v>0</v>
-      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/0282c396318842d3b4912ce2290df79c/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5b92ded873db47a283d59e744b661a0e/detail</t>
         </is>
       </c>
       <c r="P203" t="inlineStr"/>
@@ -14658,7 +13850,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>日照市卫生健康委员会内设机构分页查询服务</t>
+          <t>岚山区第二届“最美医生、最美乡医、最美护士“名单分页查询服务</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -14668,12 +13860,12 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>日照市卫生健康委员会内设机构分页查询服务</t>
+          <t>岚山区第二届“最美医生、最美乡医、最美护士“名单分页查询服务</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>日照市卫生健康委员会</t>
+          <t>日照市岚山区</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -14691,9 +13883,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I204" t="n">
-        <v>0</v>
-      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>True</t>
@@ -14705,17 +13895,15 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2231</v>
+        <v>141</v>
       </c>
       <c r="M204" t="n">
         <v>0</v>
       </c>
-      <c r="N204" t="n">
-        <v>0</v>
-      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/f8ccfce236934a8eab591ef1be0b8369/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/775ec6e3c6aa46f1bb346f27ee0c618a/detail</t>
         </is>
       </c>
       <c r="P204" t="inlineStr"/>
@@ -14728,22 +13916,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>岚山区第二届“最美医生、最美乡医、最美护士“名单分页查询服务</t>
+          <t>日照市历年工业生产者出厂价格指数分页查询服务</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>岚山区第二届“最美医生、最美乡医、最美护士“名单分页查询服务</t>
+          <t>日照市历年工业生产者出厂价格指数分页查询服务</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>日照市岚山区</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -14761,9 +13949,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I205" t="n">
-        <v>0</v>
-      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>True</t>
@@ -14775,17 +13961,15 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>138</v>
+        <v>36</v>
       </c>
       <c r="M205" t="n">
         <v>0</v>
       </c>
-      <c r="N205" t="n">
-        <v>0</v>
-      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/775ec6e3c6aa46f1bb346f27ee0c618a/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/810a0f3104cb442c85864038bcd3b91c/detail</t>
         </is>
       </c>
       <c r="P205" t="inlineStr"/>
@@ -14798,22 +13982,22 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>日照市历年工业生产者出厂价格指数分页查询服务</t>
+          <t>建筑工程施工许可证核发分页查询服务</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>日照市历年工业生产者出厂价格指数分页查询服务</t>
+          <t>建筑工程施工许可证核发分页查询服务</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市岚山区</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -14831,9 +14015,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I206" t="n">
-        <v>0</v>
-      </c>
+      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>True</t>
@@ -14845,17 +14027,15 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>35</v>
+        <v>1396</v>
       </c>
       <c r="M206" t="n">
         <v>0</v>
       </c>
-      <c r="N206" t="n">
-        <v>0</v>
-      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/810a0f3104cb442c85864038bcd3b91c/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/86494822814f4f7d97376141d62ccfdd/detail</t>
         </is>
       </c>
       <c r="P206" t="inlineStr"/>
@@ -14868,22 +14048,22 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>日照市历年一般公共预算收入分页查询服务</t>
+          <t>各乡镇派出所信息分页查询服务</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>日照市历年一般公共预算收入分页查询服务</t>
+          <t>各乡镇派出所信息分页查询服务</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市岚山区</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -14901,9 +14081,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I207" t="n">
-        <v>0</v>
-      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>True</t>
@@ -14915,17 +14093,15 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>109</v>
+        <v>4329</v>
       </c>
       <c r="M207" t="n">
         <v>0</v>
       </c>
-      <c r="N207" t="n">
-        <v>0</v>
-      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b7191a33bc9948509f84f5035d0ca7dc/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9ce0e64cf32d44a8b3e4fd0679f9b54b/detail</t>
         </is>
       </c>
       <c r="P207" t="inlineStr"/>
@@ -14938,22 +14114,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>预防接种单位信息分页查询服务</t>
+          <t>日照市年度档案技术初级职称评审通过人员名单分页查询服务</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>预防接种单位信息分页查询服务</t>
+          <t>日照市年度档案技术初级职称评审通过人员名单分页查询服务</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>日照市岚山区</t>
+          <t>日照市档案馆</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -14971,9 +14147,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I208" t="n">
-        <v>0</v>
-      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>True</t>
@@ -14985,17 +14159,15 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>419</v>
+        <v>722</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
       </c>
-      <c r="N208" t="n">
-        <v>0</v>
-      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/c2cba5cd5edb4dde81d218ade26cda9b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/ad8e89369f414122abccf2ec8d9dc0ae/detail</t>
         </is>
       </c>
       <c r="P208" t="inlineStr"/>
@@ -15008,22 +14180,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>各乡镇派出所信息分页查询服务</t>
+          <t>日照市历年农村居民人均可支配收入分页查询服务</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>各乡镇派出所信息分页查询服务</t>
+          <t>日照市历年农村居民人均可支配收入分页查询服务</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>日照市岚山区</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -15041,9 +14213,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I209" t="n">
-        <v>0</v>
-      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>True</t>
@@ -15055,17 +14225,15 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>4323</v>
+        <v>56</v>
       </c>
       <c r="M209" t="n">
         <v>0</v>
       </c>
-      <c r="N209" t="n">
-        <v>0</v>
-      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9ce0e64cf32d44a8b3e4fd0679f9b54b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/af3c482719574294ac65e69bbab9767b/detail</t>
         </is>
       </c>
       <c r="P209" t="inlineStr"/>
@@ -15078,22 +14246,22 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>日照市年度档案技术初级职称评审通过人员名单分页查询服务</t>
+          <t>日照市历年一般公共预算收入分页查询服务</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>日照市年度档案技术初级职称评审通过人员名单分页查询服务</t>
+          <t>日照市历年一般公共预算收入分页查询服务</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>日照市档案馆</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -15111,9 +14279,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I210" t="n">
-        <v>0</v>
-      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>True</t>
@@ -15125,17 +14291,15 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>717</v>
+        <v>111</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
       </c>
-      <c r="N210" t="n">
-        <v>0</v>
-      </c>
+      <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/ad8e89369f414122abccf2ec8d9dc0ae/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b7191a33bc9948509f84f5035d0ca7dc/detail</t>
         </is>
       </c>
       <c r="P210" t="inlineStr"/>
@@ -15148,22 +14312,22 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>日照市历年农村居民人均可支配收入分页查询服务</t>
+          <t>预防接种单位信息分页查询服务</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>日照市历年农村居民人均可支配收入分页查询服务</t>
+          <t>预防接种单位信息分页查询服务</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市岚山区</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -15181,9 +14345,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I211" t="n">
-        <v>0</v>
-      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>True</t>
@@ -15195,17 +14357,15 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>55</v>
+        <v>437</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
       </c>
-      <c r="N211" t="n">
-        <v>0</v>
-      </c>
+      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/af3c482719574294ac65e69bbab9767b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/c2cba5cd5edb4dde81d218ade26cda9b/detail</t>
         </is>
       </c>
       <c r="P211" t="inlineStr"/>
@@ -15218,22 +14378,22 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>各乡镇派出所信息分页查询服务</t>
+          <t>日照市卫生健康委员会内设机构分页查询服务</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>各乡镇派出所信息分页查询服务</t>
+          <t>日照市卫生健康委员会内设机构分页查询服务</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>日照市岚山区</t>
+          <t>日照市卫生健康委员会</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -15251,9 +14411,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I212" t="n">
-        <v>0</v>
-      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>True</t>
@@ -15265,17 +14423,15 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>4323</v>
+        <v>2261</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
       </c>
-      <c r="N212" t="n">
-        <v>0</v>
-      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9ce0e64cf32d44a8b3e4fd0679f9b54b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/f8ccfce236934a8eab591ef1be0b8369/detail</t>
         </is>
       </c>
       <c r="P212" t="inlineStr"/>
@@ -15288,22 +14444,22 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>农科驿站名单分页查询服务</t>
+          <t>省级服务标准化示范单位分页查询服务</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>农科驿站名单分页查询服务</t>
+          <t>省级服务标准化示范单位分页查询服务</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>日照市科学技术局</t>
+          <t>日照市市场监督管理局</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -15321,9 +14477,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I213" t="n">
-        <v>0</v>
-      </c>
+      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>True</t>
@@ -15335,17 +14489,15 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>40</v>
+        <v>546</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
       </c>
-      <c r="N213" t="n">
-        <v>0</v>
-      </c>
+      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/0d06df8d92e44eb38370334c283f0aee/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/042006ad54fe4f7ca0745b67328f4a94/detail</t>
         </is>
       </c>
       <c r="P213" t="inlineStr"/>
@@ -15358,22 +14510,22 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>日照市120指挥中心及各入网急救站联络信息分页查询服务</t>
+          <t>日照市养老机构一览表分页查询服务</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>日照市120指挥中心及各入网急救站联络信息分页查询服务</t>
+          <t>日照市养老机构一览表分页查询服务</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>日照市卫生健康委员会</t>
+          <t>日照市民政局</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -15391,9 +14543,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I214" t="n">
-        <v>0</v>
-      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>True</t>
@@ -15405,17 +14555,15 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>109</v>
+        <v>797</v>
       </c>
       <c r="M214" t="n">
         <v>0</v>
       </c>
-      <c r="N214" t="n">
-        <v>0</v>
-      </c>
+      <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/144c783285ec4b16994821e2c1eb4afb/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/0549fdbaf577454e9f22102d457ec362/detail</t>
         </is>
       </c>
       <c r="P214" t="inlineStr"/>
@@ -15428,22 +14576,22 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>日照市历年规模以上工业增加值分页查询服务</t>
+          <t>农科驿站名单分页查询服务</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>日照市历年规模以上工业增加值分页查询服务</t>
+          <t>农科驿站名单分页查询服务</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市科学技术局</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -15461,9 +14609,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I215" t="n">
-        <v>0</v>
-      </c>
+      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>True</t>
@@ -15475,17 +14621,15 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="M215" t="n">
         <v>0</v>
       </c>
-      <c r="N215" t="n">
-        <v>0</v>
-      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/19f7afbc9efe4e2ba85dfe1117eafd96/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/0d06df8d92e44eb38370334c283f0aee/detail</t>
         </is>
       </c>
       <c r="P215" t="inlineStr"/>
@@ -15498,22 +14642,22 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>日照市历年居民消费价格指数分页查询服务</t>
+          <t>日照市120指挥中心及各入网急救站联络信息分页查询服务</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>日照市历年居民消费价格指数分页查询服务</t>
+          <t>日照市120指挥中心及各入网急救站联络信息分页查询服务</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市卫生健康委员会</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -15531,9 +14675,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I216" t="n">
-        <v>0</v>
-      </c>
+      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>True</t>
@@ -15545,17 +14687,15 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M216" t="n">
         <v>0</v>
       </c>
-      <c r="N216" t="n">
-        <v>0</v>
-      </c>
+      <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1de249af368d4aab9520569a46e2d36e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/144c783285ec4b16994821e2c1eb4afb/detail</t>
         </is>
       </c>
       <c r="P216" t="inlineStr"/>
@@ -15568,7 +14708,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>日照市历年金融机构本外币存款余额分页查询服务</t>
+          <t>日照市历年规模以上工业增加值分页查询服务</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -15578,7 +14718,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>日照市历年金融机构本外币存款余额分页查询服务</t>
+          <t>日照市历年规模以上工业增加值分页查询服务</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -15601,9 +14741,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I217" t="n">
-        <v>0</v>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>True</t>
@@ -15615,17 +14753,15 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="M217" t="n">
         <v>0</v>
       </c>
-      <c r="N217" t="n">
-        <v>0</v>
-      </c>
+      <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2361734b35cd4464bbc290f213f96633/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/19f7afbc9efe4e2ba85dfe1117eafd96/detail</t>
         </is>
       </c>
       <c r="P217" t="inlineStr"/>
@@ -15638,7 +14774,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>日照市历年城镇居民人均可支配收入分页查询服务</t>
+          <t>日照市历年居民消费价格指数分页查询服务</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -15648,7 +14784,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>日照市历年城镇居民人均可支配收入分页查询服务</t>
+          <t>日照市历年居民消费价格指数分页查询服务</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -15671,9 +14807,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I218" t="n">
-        <v>0</v>
-      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>True</t>
@@ -15685,17 +14819,15 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>435</v>
+        <v>115</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
       </c>
-      <c r="N218" t="n">
-        <v>0</v>
-      </c>
+      <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3111ec199e2e43d5a5970221ef288d5b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/1de249af368d4aab9520569a46e2d36e/detail</t>
         </is>
       </c>
       <c r="P218" t="inlineStr"/>
@@ -15708,7 +14840,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>日照市历年金融机构本外币贷款余额分页查询服务</t>
+          <t>日照市历年金融机构本外币存款余额分页查询服务</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -15718,7 +14850,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>日照市历年金融机构本外币贷款余额分页查询服务</t>
+          <t>日照市历年金融机构本外币存款余额分页查询服务</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -15741,9 +14873,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I219" t="n">
-        <v>0</v>
-      </c>
+      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>True</t>
@@ -15755,17 +14885,15 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
       </c>
-      <c r="N219" t="n">
-        <v>0</v>
-      </c>
+      <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/423424571f004195bf725d2fbc433e3e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2361734b35cd4464bbc290f213f96633/detail</t>
         </is>
       </c>
       <c r="P219" t="inlineStr"/>
@@ -15778,22 +14906,22 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>流通领域成品油质量抽检公示信息分页查询服务</t>
+          <t>日照市历年城镇居民人均可支配收入分页查询服务</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>流通领域成品油质量抽检公示信息分页查询服务</t>
+          <t>日照市历年城镇居民人均可支配收入分页查询服务</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>日照市市场监督管理局</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -15811,9 +14939,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I220" t="n">
-        <v>0</v>
-      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>True</t>
@@ -15825,17 +14951,15 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>1327</v>
+        <v>441</v>
       </c>
       <c r="M220" t="n">
         <v>0</v>
       </c>
-      <c r="N220" t="n">
-        <v>0</v>
-      </c>
+      <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/4be990065967427fae5a59fec900ee9f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/3111ec199e2e43d5a5970221ef288d5b/detail</t>
         </is>
       </c>
       <c r="P220" t="inlineStr"/>
@@ -15848,22 +14972,22 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>日照市年度档案技术中级职称评审通过人员名单分页查询服务</t>
+          <t>日照市历年金融机构本外币贷款余额分页查询服务</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>日照市年度档案技术中级职称评审通过人员名单分页查询服务</t>
+          <t>日照市历年金融机构本外币贷款余额分页查询服务</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>日照市档案馆</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -15881,9 +15005,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I221" t="n">
-        <v>0</v>
-      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
           <t>True</t>
@@ -15895,17 +15017,15 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>1631</v>
+        <v>27</v>
       </c>
       <c r="M221" t="n">
         <v>0</v>
       </c>
-      <c r="N221" t="n">
-        <v>0</v>
-      </c>
+      <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/4ca36641216a47d78f0d9448ed94bf77/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/423424571f004195bf725d2fbc433e3e/detail</t>
         </is>
       </c>
       <c r="P221" t="inlineStr"/>
@@ -15918,7 +15038,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>日照市历年城镇居民人均可支配收入分页查询服务</t>
+          <t>日照市历年规模以上工业增加值分页查询服务</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -15928,7 +15048,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>日照市历年城镇居民人均可支配收入分页查询服务</t>
+          <t>日照市历年规模以上工业增加值分页查询服务</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -15951,9 +15071,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I222" t="n">
-        <v>0</v>
-      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>True</t>
@@ -15965,17 +15083,15 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>435</v>
+        <v>115</v>
       </c>
       <c r="M222" t="n">
         <v>0</v>
       </c>
-      <c r="N222" t="n">
-        <v>0</v>
-      </c>
+      <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3111ec199e2e43d5a5970221ef288d5b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/19f7afbc9efe4e2ba85dfe1117eafd96/detail</t>
         </is>
       </c>
       <c r="P222" t="inlineStr"/>
@@ -15988,7 +15104,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>日照市历年金融机构本外币贷款余额分页查询服务</t>
+          <t>日照市历年居民消费价格指数分页查询服务</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -15998,7 +15114,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>日照市历年金融机构本外币贷款余额分页查询服务</t>
+          <t>日照市历年居民消费价格指数分页查询服务</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -16021,9 +15137,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I223" t="n">
-        <v>0</v>
-      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>True</t>
@@ -16035,17 +15149,15 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="M223" t="n">
         <v>0</v>
       </c>
-      <c r="N223" t="n">
-        <v>0</v>
-      </c>
+      <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/423424571f004195bf725d2fbc433e3e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/1de249af368d4aab9520569a46e2d36e/detail</t>
         </is>
       </c>
       <c r="P223" t="inlineStr"/>
@@ -16058,22 +15170,22 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>流通领域成品油质量抽检公示信息分页查询服务</t>
+          <t>日照市历年金融机构本外币存款余额分页查询服务</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>流通领域成品油质量抽检公示信息分页查询服务</t>
+          <t>日照市历年金融机构本外币存款余额分页查询服务</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>日照市市场监督管理局</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -16091,9 +15203,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I224" t="n">
-        <v>0</v>
-      </c>
+      <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
           <t>True</t>
@@ -16105,17 +15215,15 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1327</v>
+        <v>35</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
       </c>
-      <c r="N224" t="n">
-        <v>0</v>
-      </c>
+      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/4be990065967427fae5a59fec900ee9f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2361734b35cd4464bbc290f213f96633/detail</t>
         </is>
       </c>
       <c r="P224" t="inlineStr"/>
@@ -16128,22 +15236,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>日照市年度档案技术中级职称评审通过人员名单分页查询服务</t>
+          <t>市审计局信息公开目录分页查询服务</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>日照市年度档案技术中级职称评审通过人员名单分页查询服务</t>
+          <t>市审计局信息公开目录分页查询服务</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>日照市档案馆</t>
+          <t>日照市审计局</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -16161,9 +15269,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I225" t="n">
-        <v>0</v>
-      </c>
+      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>True</t>
@@ -16175,17 +15281,15 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1631</v>
+        <v>114</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
-      </c>
-      <c r="N225" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/4ca36641216a47d78f0d9448ed94bf77/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5d5076b8e7f741e0a51be180f3a06a62/detail</t>
         </is>
       </c>
       <c r="P225" t="inlineStr"/>
@@ -16198,22 +15302,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>日照市典当行业名单分页查询服务</t>
+          <t>日照市历年在岗职工平均工资分页查询服务</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>日照市典当行业名单分页查询服务</t>
+          <t>日照市历年在岗职工平均工资分页查询服务</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>日照市商务局</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -16231,9 +15335,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I226" t="n">
-        <v>0</v>
-      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>True</t>
@@ -16245,17 +15347,15 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="M226" t="n">
         <v>0</v>
       </c>
-      <c r="N226" t="n">
-        <v>0</v>
-      </c>
+      <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a2686680798444c0aec89d126adf119c/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5f4780ef9e9c41a1aec4f46fc6bdd8d8/detail</t>
         </is>
       </c>
       <c r="P226" t="inlineStr"/>
@@ -16268,22 +15368,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>岚山区幼儿园名单分页查询服务</t>
+          <t>省级服务标准化示范单位分页查询服务</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>岚山区幼儿园名单分页查询服务</t>
+          <t>省级服务标准化示范单位分页查询服务</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>日照市岚山区</t>
+          <t>日照市市场监督管理局</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -16301,9 +15401,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I227" t="n">
-        <v>0</v>
-      </c>
+      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>True</t>
@@ -16315,17 +15413,15 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>4985</v>
+        <v>546</v>
       </c>
       <c r="M227" t="n">
         <v>0</v>
       </c>
-      <c r="N227" t="n">
-        <v>0</v>
-      </c>
+      <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/8ed7655b0d0c42a091e9c6da43741692/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/042006ad54fe4f7ca0745b67328f4a94/detail</t>
         </is>
       </c>
       <c r="P227" t="inlineStr"/>
@@ -16338,22 +15434,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>日照市历年粮食总产量分页查询服务</t>
+          <t>日照市养老机构一览表分页查询服务</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>日照市历年粮食总产量分页查询服务</t>
+          <t>日照市养老机构一览表分页查询服务</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市民政局</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -16371,9 +15467,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I228" t="n">
-        <v>0</v>
-      </c>
+      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>True</t>
@@ -16385,17 +15479,15 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>97</v>
+        <v>797</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
       </c>
-      <c r="N228" t="n">
-        <v>0</v>
-      </c>
+      <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/99dad31664644057b28940ca0526ac46/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/0549fdbaf577454e9f22102d457ec362/detail</t>
         </is>
       </c>
       <c r="P228" t="inlineStr"/>
@@ -16408,22 +15500,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>市审计局信息公开目录分页查询服务</t>
+          <t>科技成果登记信息分页查询服务</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>市审计局信息公开目录分页查询服务</t>
+          <t>科技成果登记信息分页查询服务</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>日照市审计局</t>
+          <t>日照市科学技术局</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -16441,9 +15533,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I229" t="n">
-        <v>0</v>
-      </c>
+      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>True</t>
@@ -16455,17 +15545,15 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M229" t="n">
-        <v>1</v>
-      </c>
-      <c r="N229" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5d5076b8e7f741e0a51be180f3a06a62/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/cb8e1db4af9546498936a8a9ebcd480a/detail</t>
         </is>
       </c>
       <c r="P229" t="inlineStr"/>
@@ -16478,22 +15566,22 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>日照市历年在岗职工平均工资分页查询服务</t>
+          <t>市财政局信息公开目录分页查询服务</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>财税金融</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>日照市历年在岗职工平均工资分页查询服务</t>
+          <t>市财政局信息公开目录分页查询服务</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市财政局</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -16511,9 +15599,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I230" t="n">
-        <v>0</v>
-      </c>
+      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>True</t>
@@ -16525,17 +15611,15 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
-      </c>
-      <c r="N230" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5f4780ef9e9c41a1aec4f46fc6bdd8d8/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/ccc272533b2f42aa9a8b96aadd3e29ea/detail</t>
         </is>
       </c>
       <c r="P230" t="inlineStr"/>
@@ -16548,22 +15632,22 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>日照市历年进出口总值分页查询服务</t>
+          <t>日照市公立医院名录分页查询服务</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>日照市历年进出口总值分页查询服务</t>
+          <t>日照市公立医院名录分页查询服务</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市卫生健康委员会</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -16581,9 +15665,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I231" t="n">
-        <v>0</v>
-      </c>
+      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>True</t>
@@ -16595,17 +15677,15 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
       </c>
-      <c r="N231" t="n">
-        <v>0</v>
-      </c>
+      <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/448aabd1504249738d9bb92070f14963/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/068b48de65af4582a1966f7aa82cea23/detail</t>
         </is>
       </c>
       <c r="P231" t="inlineStr"/>
@@ -16618,22 +15698,22 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>流通领域农资质量抽检公示信息分页查询服务</t>
+          <t>日照市历年一般公共预算支出分页查询服务</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>流通领域农资质量抽检公示信息分页查询服务</t>
+          <t>日照市历年一般公共预算支出分页查询服务</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>日照市市场监督管理局</t>
+          <t>日照市统计局</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -16651,9 +15731,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I232" t="n">
-        <v>0</v>
-      </c>
+      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>True</t>
@@ -16665,17 +15743,15 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>1607</v>
+        <v>26</v>
       </c>
       <c r="M232" t="n">
         <v>0</v>
       </c>
-      <c r="N232" t="n">
-        <v>0</v>
-      </c>
+      <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5b30dc2b7c8044a490aab7a132350ccc/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/312d479e2ed243d080c5d1f16a002927/detail</t>
         </is>
       </c>
       <c r="P232" t="inlineStr"/>
@@ -16688,7 +15764,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>日照市历年一般公共预算支出分页查询服务</t>
+          <t>日照市历年进出口总值分页查询服务</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -16698,7 +15774,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>日照市历年一般公共预算支出分页查询服务</t>
+          <t>日照市历年进出口总值分页查询服务</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -16721,9 +15797,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I233" t="n">
-        <v>0</v>
-      </c>
+      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>True</t>
@@ -16735,17 +15809,15 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
       </c>
-      <c r="N233" t="n">
-        <v>0</v>
-      </c>
+      <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/312d479e2ed243d080c5d1f16a002927/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/448aabd1504249738d9bb92070f14963/detail</t>
         </is>
       </c>
       <c r="P233" t="inlineStr"/>
@@ -16758,22 +15830,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>日照市历年进出口总值分页查询服务</t>
+          <t>流通领域农资质量抽检公示信息分页查询服务</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>日照市历年进出口总值分页查询服务</t>
+          <t>流通领域农资质量抽检公示信息分页查询服务</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>日照市统计局</t>
+          <t>日照市市场监督管理局</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -16791,9 +15863,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I234" t="n">
-        <v>0</v>
-      </c>
+      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>True</t>
@@ -16805,17 +15875,15 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>136</v>
+        <v>1644</v>
       </c>
       <c r="M234" t="n">
         <v>0</v>
       </c>
-      <c r="N234" t="n">
-        <v>0</v>
-      </c>
+      <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/448aabd1504249738d9bb92070f14963/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5b30dc2b7c8044a490aab7a132350ccc/detail</t>
         </is>
       </c>
       <c r="P234" t="inlineStr"/>
@@ -16857,9 +15925,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I235" t="n">
-        <v>0</v>
-      </c>
+      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>True</t>
@@ -16871,14 +15937,12 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>1038</v>
+        <v>1068</v>
       </c>
       <c r="M235" t="n">
         <v>1</v>
       </c>
-      <c r="N235" t="n">
-        <v>0</v>
-      </c>
+      <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/8a78dbb800a941ada1431e019b062aaa/detail</t>
@@ -16927,9 +15991,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I236" t="n">
-        <v>0</v>
-      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>True</t>
@@ -16941,14 +16003,12 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="M236" t="n">
         <v>0</v>
       </c>
-      <c r="N236" t="n">
-        <v>0</v>
-      </c>
+      <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/fd60a473a50e42af8f5b067dcbf6414e/detail</t>
